--- a/histograms/histogram_Average_Mulliken_electronegativity.xlsx
+++ b/histograms/histogram_Average_Mulliken_electronegativity.xlsx
@@ -445,7 +445,7 @@
         <v>5.615783621390046</v>
       </c>
       <c r="B2" t="n">
-        <v>306</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3">
@@ -453,7 +453,7 @@
         <v>5.676364296170137</v>
       </c>
       <c r="B3" t="n">
-        <v>471</v>
+        <v>41</v>
       </c>
     </row>
     <row r="4">
@@ -461,7 +461,7 @@
         <v>5.736944970950228</v>
       </c>
       <c r="B4" t="n">
-        <v>144</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
@@ -469,7 +469,7 @@
         <v>5.797525645730319</v>
       </c>
       <c r="B5" t="n">
-        <v>231</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6">
@@ -477,7 +477,7 @@
         <v>5.85810632051041</v>
       </c>
       <c r="B6" t="n">
-        <v>117</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -485,7 +485,7 @@
         <v>5.918686995290502</v>
       </c>
       <c r="B7" t="n">
-        <v>735</v>
+        <v>43</v>
       </c>
     </row>
     <row r="8">
@@ -493,7 +493,7 @@
         <v>5.979267670070593</v>
       </c>
       <c r="B8" t="n">
-        <v>4477</v>
+        <v>155</v>
       </c>
     </row>
     <row r="9">
@@ -501,7 +501,7 @@
         <v>6.039848344850684</v>
       </c>
       <c r="B9" t="n">
-        <v>649</v>
+        <v>37</v>
       </c>
     </row>
     <row r="10">
@@ -509,7 +509,7 @@
         <v>6.100429019630775</v>
       </c>
       <c r="B10" t="n">
-        <v>2502</v>
+        <v>30</v>
       </c>
     </row>
     <row r="11">
@@ -517,7 +517,7 @@
         <v>6.161009694410867</v>
       </c>
       <c r="B11" t="n">
-        <v>2848</v>
+        <v>54</v>
       </c>
     </row>
     <row r="12">
@@ -525,7 +525,7 @@
         <v>6.221590369190958</v>
       </c>
       <c r="B12" t="n">
-        <v>3328</v>
+        <v>72</v>
       </c>
     </row>
     <row r="13">
@@ -533,7 +533,7 @@
         <v>6.282171043971049</v>
       </c>
       <c r="B13" t="n">
-        <v>2810</v>
+        <v>74</v>
       </c>
     </row>
     <row r="14">
@@ -541,7 +541,7 @@
         <v>6.34275171875114</v>
       </c>
       <c r="B14" t="n">
-        <v>80</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15">
@@ -549,7 +549,7 @@
         <v>6.403332393531231</v>
       </c>
       <c r="B15" t="n">
-        <v>548</v>
+        <v>34</v>
       </c>
     </row>
     <row r="16">
@@ -557,7 +557,7 @@
         <v>6.463913068311323</v>
       </c>
       <c r="B16" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17">
@@ -565,7 +565,7 @@
         <v>6.524493743091414</v>
       </c>
       <c r="B17" t="n">
-        <v>599</v>
+        <v>5</v>
       </c>
     </row>
     <row r="18">
@@ -573,7 +573,7 @@
         <v>6.585074417871505</v>
       </c>
       <c r="B18" t="n">
-        <v>359</v>
+        <v>9</v>
       </c>
     </row>
     <row r="19">
@@ -581,7 +581,7 @@
         <v>6.645655092651596</v>
       </c>
       <c r="B19" t="n">
-        <v>1408</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20">
@@ -589,7 +589,7 @@
         <v>6.706235767431687</v>
       </c>
       <c r="B20" t="n">
-        <v>2959</v>
+        <v>81</v>
       </c>
     </row>
     <row r="21">
@@ -597,7 +597,7 @@
         <v>6.766816442211779</v>
       </c>
       <c r="B21" t="n">
-        <v>1815</v>
+        <v>41</v>
       </c>
     </row>
   </sheetData>
